--- a/data/reports/PHASE_5_SUM_ENGINE.xlsx
+++ b/data/reports/PHASE_5_SUM_ENGINE.xlsx
@@ -443,7 +443,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
@@ -499,7 +499,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -1132,7 +1132,7 @@
         <v>11</v>
       </c>
       <c r="C35" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36">
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,15 +1423,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B4" t="n">
         <v>3</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
         <v>3</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -1487,7 +1487,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -1495,7 +1495,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" t="n">
         <v>1</v>
@@ -1543,7 +1543,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
@@ -1551,9 +1551,17 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>25</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1588,7 +1596,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1689,10 +1697,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1713,7 +1721,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
@@ -1721,7 +1729,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -1811,7 +1819,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" t="n">
         <v>6</v>
@@ -1819,7 +1827,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>6</v>
@@ -1827,7 +1835,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>6</v>
@@ -1835,10 +1843,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1867,7 +1875,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -1875,15 +1883,15 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
@@ -2021,7 +2029,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
         <v>10</v>
@@ -2037,10 +2045,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2061,15 +2069,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="n">
         <v>8</v>
-      </c>
-      <c r="B14" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
         <v>7</v>
@@ -2186,7 +2194,7 @@
         <v>1088</v>
       </c>
       <c r="D2" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3">
@@ -2200,7 +2208,7 @@
         <v>1195</v>
       </c>
       <c r="D3" t="n">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4">
@@ -2214,7 +2222,7 @@
         <v>1248</v>
       </c>
       <c r="D4" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5">
@@ -2228,7 +2236,7 @@
         <v>1302</v>
       </c>
       <c r="D5" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6">
@@ -2242,7 +2250,7 @@
         <v>1399</v>
       </c>
       <c r="D6" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7">
@@ -2256,7 +2264,7 @@
         <v>1519</v>
       </c>
       <c r="D7" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
@@ -2270,7 +2278,7 @@
         <v>1609</v>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
@@ -2284,88 +2292,88 @@
         <v>1674</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="C10" t="n">
-        <v>1702</v>
+        <v>1708</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="C11" t="n">
-        <v>1708</v>
+        <v>1724</v>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46155</v>
+        <v>46159</v>
       </c>
       <c r="C12" t="n">
-        <v>1724</v>
+        <v>1732</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="C13" t="n">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C14" t="n">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C15" t="n">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="D15" t="n">
         <v>17</v>
@@ -2373,69 +2381,69 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>46163</v>
       </c>
       <c r="C16" t="n">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C17" t="n">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="C18" t="n">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C19" t="n">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C20" t="n">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2443,13 +2451,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="C21" t="n">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -2457,13 +2465,13 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="C22" t="n">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="D22" t="n">
         <v>8</v>
@@ -2471,41 +2479,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="C23" t="n">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C24" t="n">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="C25" t="n">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -2513,13 +2521,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C26" t="n">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -2527,13 +2535,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="C27" t="n">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
@@ -2541,13 +2549,13 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C28" t="n">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -2555,13 +2563,13 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="C29" t="n">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
